--- a/Reporte_ventas/Colores excel para materiales.xlsx
+++ b/Reporte_ventas/Colores excel para materiales.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Valeria\Reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maval\Documents\Vale laburo\Castelli\Reportes\Reporte_ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>ROJO</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>OLIVE</t>
+  </si>
+  <si>
+    <t>HEREFORD/TABACO</t>
   </si>
 </sst>
 </file>
@@ -395,18 +398,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -420,7 +423,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -434,7 +437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -448,7 +451,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -462,7 +465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -476,7 +479,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -490,7 +493,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -504,7 +507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -518,7 +521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -532,7 +535,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -546,7 +549,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -560,7 +563,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -574,7 +577,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -588,7 +591,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -602,7 +605,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -616,7 +619,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -630,7 +633,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -642,6 +645,20 @@
       </c>
       <c r="D19">
         <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>89</v>
+      </c>
+      <c r="C20">
+        <v>59</v>
+      </c>
+      <c r="D20">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Reporte_ventas/Colores excel para materiales.xlsx
+++ b/Reporte_ventas/Colores excel para materiales.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>ROJO</t>
   </si>
@@ -81,6 +81,18 @@
   </si>
   <si>
     <t>HEREFORD/TABACO</t>
+  </si>
+  <si>
+    <t>BRONCE</t>
+  </si>
+  <si>
+    <t>GRIS OSCURO</t>
+  </si>
+  <si>
+    <t>PLATINUM</t>
+  </si>
+  <si>
+    <t>CAOBA</t>
   </si>
 </sst>
 </file>
@@ -398,18 +410,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -423,7 +435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -437,7 +449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -451,7 +463,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -465,7 +477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -479,7 +491,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -493,7 +505,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -507,7 +519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -521,7 +533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -535,7 +547,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -549,7 +561,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -563,7 +575,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -577,7 +589,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -591,7 +603,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -605,7 +617,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -619,7 +631,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -633,7 +645,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -647,7 +659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -659,6 +671,62 @@
       </c>
       <c r="D20">
         <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>205</v>
+      </c>
+      <c r="C21">
+        <v>127</v>
+      </c>
+      <c r="D21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>127</v>
+      </c>
+      <c r="C22">
+        <v>127</v>
+      </c>
+      <c r="D22">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>192</v>
+      </c>
+      <c r="C23">
+        <v>192</v>
+      </c>
+      <c r="D23">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>192</v>
+      </c>
+      <c r="C24">
+        <v>64</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Reporte_ventas/Colores excel para materiales.xlsx
+++ b/Reporte_ventas/Colores excel para materiales.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -12,9 +12,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>ROJO</t>
   </si>
@@ -98,8 +97,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,7 +134,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -409,8 +407,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
@@ -729,6 +727,86 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NEGRO</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BRONZE</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>205</v>
+      </c>
+      <c r="C26">
+        <v>127</v>
+      </c>
+      <c r="D26">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SAPPHIRE</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>82</v>
+      </c>
+      <c r="D27">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AVELLANA</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>194</v>
+      </c>
+      <c r="C28">
+        <v>154</v>
+      </c>
+      <c r="D28">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OXIDO</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>153</v>
+      </c>
+      <c r="C29">
+        <v>51</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
